--- a/scripts/Fig2/nolabel.xlsx
+++ b/scripts/Fig2/nolabel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\周泽铭\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8449E2C-9D47-416C-BBB2-35AC15E6A2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327056EE-BF73-4DC4-8475-69C53A67207C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -134,6 +134,18 @@
   </si>
   <si>
     <t>**</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>*</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>**</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ns</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -605,14 +617,14 @@
       <c r="J3" s="1">
         <v>46555</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>15</v>
+      <c r="K3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -769,11 +781,11 @@
       <c r="J7" s="1">
         <v>3266</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>17</v>
+      <c r="K7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>15</v>
@@ -813,8 +825,8 @@
       <c r="K8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>15</v>
+      <c r="L8" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>15</v>
@@ -892,8 +904,8 @@
       <c r="J10" s="1">
         <v>1767</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>15</v>
+      <c r="K10" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>24</v>
@@ -933,8 +945,8 @@
       <c r="J11" s="1">
         <v>1039</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>17</v>
+      <c r="K11" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>15</v>
@@ -1015,11 +1027,11 @@
       <c r="J13" s="1">
         <v>1980</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>17</v>
+      <c r="K13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>15</v>
@@ -1059,8 +1071,8 @@
       <c r="K14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>15</v>
+      <c r="L14" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>15</v>
@@ -1097,8 +1109,8 @@
       <c r="J15" s="1">
         <v>7776</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>17</v>
+      <c r="K15" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>17</v>
@@ -1220,8 +1232,8 @@
       <c r="J18" s="1">
         <v>12749.333000000001</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>27</v>
+      <c r="K18" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>17</v>
@@ -1302,8 +1314,8 @@
       <c r="J20" s="1">
         <v>588752.34620000003</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>27</v>
+      <c r="K20" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>27</v>
@@ -1343,8 +1355,8 @@
       <c r="J21" s="1">
         <v>1003.5334</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>17</v>
+      <c r="K21" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>15</v>
